--- a/output/upload/S00026_1833_Wealth직장인연금보험_무배당.xlsx
+++ b/output/upload/S00026_1833_Wealth직장인연금보험_무배당.xlsx
@@ -12485,22 +12485,22 @@
     <row r="187">
       <c r="B187" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -12544,22 +12544,22 @@
     <row r="188">
       <c r="B188" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -12603,22 +12603,22 @@
     <row r="189">
       <c r="B189" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -12662,22 +12662,22 @@
     <row r="190">
       <c r="B190" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -12721,22 +12721,22 @@
     <row r="191">
       <c r="B191" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -12780,22 +12780,22 @@
     <row r="192">
       <c r="B192" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -12839,22 +12839,22 @@
     <row r="193">
       <c r="B193" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -12898,22 +12898,22 @@
     <row r="194">
       <c r="B194" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -12957,22 +12957,22 @@
     <row r="195">
       <c r="B195" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -13016,22 +13016,22 @@
     <row r="196">
       <c r="B196" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -13075,22 +13075,22 @@
     <row r="197">
       <c r="B197" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -13134,22 +13134,22 @@
     <row r="198">
       <c r="B198" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -13193,22 +13193,22 @@
     <row r="199">
       <c r="B199" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -13252,22 +13252,22 @@
     <row r="200">
       <c r="B200" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -13311,22 +13311,22 @@
     <row r="201">
       <c r="B201" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -13370,22 +13370,22 @@
     <row r="202">
       <c r="B202" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -13429,22 +13429,22 @@
     <row r="203">
       <c r="B203" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -13488,22 +13488,22 @@
     <row r="204">
       <c r="B204" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -13547,22 +13547,22 @@
     <row r="205">
       <c r="B205" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -13606,22 +13606,22 @@
     <row r="206">
       <c r="B206" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -13665,22 +13665,22 @@
     <row r="207">
       <c r="B207" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
@@ -13724,22 +13724,22 @@
     <row r="208">
       <c r="B208" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -13783,22 +13783,22 @@
     <row r="209">
       <c r="B209" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -13842,22 +13842,22 @@
     <row r="210">
       <c r="B210" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -13901,22 +13901,22 @@
     <row r="211">
       <c r="B211" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -13960,22 +13960,22 @@
     <row r="212">
       <c r="B212" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -14019,22 +14019,22 @@
     <row r="213">
       <c r="B213" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -14078,22 +14078,22 @@
     <row r="214">
       <c r="B214" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -14137,22 +14137,22 @@
     <row r="215">
       <c r="B215" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -14196,22 +14196,22 @@
     <row r="216">
       <c r="B216" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -14255,22 +14255,22 @@
     <row r="217">
       <c r="B217" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -14314,22 +14314,22 @@
     <row r="218">
       <c r="B218" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -14373,22 +14373,22 @@
     <row r="219">
       <c r="B219" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -14432,22 +14432,22 @@
     <row r="220">
       <c r="B220" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -14491,22 +14491,22 @@
     <row r="221">
       <c r="B221" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -14550,22 +14550,22 @@
     <row r="222">
       <c r="B222" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
@@ -14609,22 +14609,22 @@
     <row r="223">
       <c r="B223" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
@@ -14668,22 +14668,22 @@
     <row r="224">
       <c r="B224" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
@@ -14727,22 +14727,22 @@
     <row r="225">
       <c r="B225" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -14786,22 +14786,22 @@
     <row r="226">
       <c r="B226" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
@@ -14845,22 +14845,22 @@
     <row r="227">
       <c r="B227" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
@@ -14904,22 +14904,22 @@
     <row r="228">
       <c r="B228" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
@@ -14963,22 +14963,22 @@
     <row r="229">
       <c r="B229" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
@@ -15022,22 +15022,22 @@
     <row r="230">
       <c r="B230" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
@@ -15081,22 +15081,22 @@
     <row r="231">
       <c r="B231" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
@@ -15140,22 +15140,22 @@
     <row r="232">
       <c r="B232" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -15199,22 +15199,22 @@
     <row r="233">
       <c r="B233" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -15258,22 +15258,22 @@
     <row r="234">
       <c r="B234" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -15317,22 +15317,22 @@
     <row r="235">
       <c r="B235" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
@@ -15376,22 +15376,22 @@
     <row r="236">
       <c r="B236" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
@@ -15435,22 +15435,22 @@
     <row r="237">
       <c r="B237" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -15494,22 +15494,22 @@
     <row r="238">
       <c r="B238" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -15553,22 +15553,22 @@
     <row r="239">
       <c r="B239" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
@@ -15612,22 +15612,22 @@
     <row r="240">
       <c r="B240" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -15671,22 +15671,22 @@
     <row r="241">
       <c r="B241" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -15730,22 +15730,22 @@
     <row r="242">
       <c r="B242" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
@@ -15789,22 +15789,22 @@
     <row r="243">
       <c r="B243" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
@@ -15848,22 +15848,22 @@
     <row r="244">
       <c r="B244" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
@@ -15907,22 +15907,22 @@
     <row r="245">
       <c r="B245" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -15966,22 +15966,22 @@
     <row r="246">
       <c r="B246" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -16025,22 +16025,22 @@
     <row r="247">
       <c r="B247" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -16084,22 +16084,22 @@
     <row r="248">
       <c r="B248" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -16143,22 +16143,22 @@
     <row r="249">
       <c r="B249" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -16202,22 +16202,22 @@
     <row r="250">
       <c r="B250" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -16261,22 +16261,22 @@
     <row r="251">
       <c r="B251" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -16320,22 +16320,22 @@
     <row r="252">
       <c r="B252" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -16379,22 +16379,22 @@
     <row r="253">
       <c r="B253" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -16438,22 +16438,22 @@
     <row r="254">
       <c r="B254" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -16497,22 +16497,22 @@
     <row r="255">
       <c r="B255" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -16556,22 +16556,22 @@
     <row r="256">
       <c r="B256" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -16615,22 +16615,22 @@
     <row r="257">
       <c r="B257" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -16674,22 +16674,22 @@
     <row r="258">
       <c r="B258" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16733,22 +16733,22 @@
     <row r="259">
       <c r="B259" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -16792,22 +16792,22 @@
     <row r="260">
       <c r="B260" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
@@ -16851,22 +16851,22 @@
     <row r="261">
       <c r="B261" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
@@ -16910,22 +16910,22 @@
     <row r="262">
       <c r="B262" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
@@ -16969,22 +16969,22 @@
     <row r="263">
       <c r="B263" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F263" t="inlineStr">
@@ -17028,22 +17028,22 @@
     <row r="264">
       <c r="B264" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -17087,22 +17087,22 @@
     <row r="265">
       <c r="B265" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
@@ -17146,22 +17146,22 @@
     <row r="266">
       <c r="B266" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
@@ -17205,22 +17205,22 @@
     <row r="267">
       <c r="B267" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -17264,22 +17264,22 @@
     <row r="268">
       <c r="B268" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -17323,22 +17323,22 @@
     <row r="269">
       <c r="B269" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -17382,22 +17382,22 @@
     <row r="270">
       <c r="B270" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -17441,22 +17441,22 @@
     <row r="271">
       <c r="B271" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
@@ -17500,22 +17500,22 @@
     <row r="272">
       <c r="B272" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
@@ -17559,22 +17559,22 @@
     <row r="273">
       <c r="B273" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -17618,22 +17618,22 @@
     <row r="274">
       <c r="B274" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -17677,22 +17677,22 @@
     <row r="275">
       <c r="B275" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
@@ -17736,22 +17736,22 @@
     <row r="276">
       <c r="B276" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -17795,22 +17795,22 @@
     <row r="277">
       <c r="B277" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -17854,22 +17854,22 @@
     <row r="278">
       <c r="B278" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
@@ -17913,22 +17913,22 @@
     <row r="279">
       <c r="B279" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
@@ -17972,22 +17972,22 @@
     <row r="280">
       <c r="B280" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -18031,22 +18031,22 @@
     <row r="281">
       <c r="B281" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -18090,22 +18090,22 @@
     <row r="282">
       <c r="B282" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -18149,22 +18149,22 @@
     <row r="283">
       <c r="B283" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -18208,22 +18208,22 @@
     <row r="284">
       <c r="B284" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -18267,22 +18267,22 @@
     <row r="285">
       <c r="B285" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -18326,22 +18326,22 @@
     <row r="286">
       <c r="B286" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -18385,22 +18385,22 @@
     <row r="287">
       <c r="B287" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -18444,22 +18444,22 @@
     <row r="288">
       <c r="B288" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -18503,22 +18503,22 @@
     <row r="289">
       <c r="B289" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -18562,22 +18562,22 @@
     <row r="290">
       <c r="B290" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -18621,22 +18621,22 @@
     <row r="291">
       <c r="B291" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -18680,22 +18680,22 @@
     <row r="292">
       <c r="B292" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -18739,22 +18739,22 @@
     <row r="293">
       <c r="B293" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -18798,22 +18798,22 @@
     <row r="294">
       <c r="B294" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
@@ -18857,22 +18857,22 @@
     <row r="295">
       <c r="B295" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
@@ -18916,22 +18916,22 @@
     <row r="296">
       <c r="B296" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
@@ -18975,22 +18975,22 @@
     <row r="297">
       <c r="B297" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
@@ -19034,22 +19034,22 @@
     <row r="298">
       <c r="B298" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
@@ -19093,22 +19093,22 @@
     <row r="299">
       <c r="B299" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
@@ -19152,22 +19152,22 @@
     <row r="300">
       <c r="B300" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
@@ -19211,22 +19211,22 @@
     <row r="301">
       <c r="B301" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
@@ -19270,22 +19270,22 @@
     <row r="302">
       <c r="B302" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -19329,22 +19329,22 @@
     <row r="303">
       <c r="B303" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
@@ -19388,22 +19388,22 @@
     <row r="304">
       <c r="B304" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -19447,22 +19447,22 @@
     <row r="305">
       <c r="B305" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -19506,22 +19506,22 @@
     <row r="306">
       <c r="B306" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -19565,22 +19565,22 @@
     <row r="307">
       <c r="B307" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
@@ -19624,22 +19624,22 @@
     <row r="308">
       <c r="B308" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -19683,22 +19683,22 @@
     <row r="309">
       <c r="B309" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
@@ -19742,22 +19742,22 @@
     <row r="310">
       <c r="B310" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
@@ -19801,22 +19801,22 @@
     <row r="311">
       <c r="B311" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
@@ -19860,22 +19860,22 @@
     <row r="312">
       <c r="B312" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -19919,22 +19919,22 @@
     <row r="313">
       <c r="B313" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -19978,22 +19978,22 @@
     <row r="314">
       <c r="B314" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
@@ -20037,22 +20037,22 @@
     <row r="315">
       <c r="B315" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
@@ -20096,22 +20096,22 @@
     <row r="316">
       <c r="B316" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
@@ -20155,22 +20155,22 @@
     <row r="317">
       <c r="B317" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -20214,22 +20214,22 @@
     <row r="318">
       <c r="B318" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -20273,22 +20273,22 @@
     <row r="319">
       <c r="B319" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -20332,22 +20332,22 @@
     <row r="320">
       <c r="B320" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -20391,22 +20391,22 @@
     <row r="321">
       <c r="B321" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -20450,22 +20450,22 @@
     <row r="322">
       <c r="B322" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -20509,22 +20509,22 @@
     <row r="323">
       <c r="B323" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -20568,22 +20568,22 @@
     <row r="324">
       <c r="B324" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -20627,22 +20627,22 @@
     <row r="325">
       <c r="B325" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -20686,22 +20686,22 @@
     <row r="326">
       <c r="B326" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -20745,22 +20745,22 @@
     <row r="327">
       <c r="B327" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -20804,22 +20804,22 @@
     <row r="328">
       <c r="B328" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -20863,22 +20863,22 @@
     <row r="329">
       <c r="B329" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
@@ -20922,22 +20922,22 @@
     <row r="330">
       <c r="B330" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
@@ -20981,22 +20981,22 @@
     <row r="331">
       <c r="B331" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
@@ -21040,22 +21040,22 @@
     <row r="332">
       <c r="B332" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F332" t="inlineStr">
@@ -21099,22 +21099,22 @@
     <row r="333">
       <c r="B333" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F333" t="inlineStr">
@@ -21158,22 +21158,22 @@
     <row r="334">
       <c r="B334" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F334" t="inlineStr">
@@ -21217,22 +21217,22 @@
     <row r="335">
       <c r="B335" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
@@ -21276,22 +21276,22 @@
     <row r="336">
       <c r="B336" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
@@ -21335,22 +21335,22 @@
     <row r="337">
       <c r="B337" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
@@ -21394,22 +21394,22 @@
     <row r="338">
       <c r="B338" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
@@ -21453,22 +21453,22 @@
     <row r="339">
       <c r="B339" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
@@ -21512,22 +21512,22 @@
     <row r="340">
       <c r="B340" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
@@ -21571,22 +21571,22 @@
     <row r="341">
       <c r="B341" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
@@ -21630,22 +21630,22 @@
     <row r="342">
       <c r="B342" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
@@ -21689,22 +21689,22 @@
     <row r="343">
       <c r="B343" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
@@ -21748,22 +21748,22 @@
     <row r="344">
       <c r="B344" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
@@ -21807,22 +21807,22 @@
     <row r="345">
       <c r="B345" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
@@ -21866,22 +21866,22 @@
     <row r="346">
       <c r="B346" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
@@ -21925,22 +21925,22 @@
     <row r="347">
       <c r="B347" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F347" t="inlineStr">
@@ -21984,22 +21984,22 @@
     <row r="348">
       <c r="B348" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
@@ -22043,22 +22043,22 @@
     <row r="349">
       <c r="B349" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
@@ -22102,22 +22102,22 @@
     <row r="350">
       <c r="B350" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
@@ -22161,22 +22161,22 @@
     <row r="351">
       <c r="B351" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
@@ -22220,22 +22220,22 @@
     <row r="352">
       <c r="B352" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
@@ -22279,22 +22279,22 @@
     <row r="353">
       <c r="B353" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
@@ -22338,22 +22338,22 @@
     <row r="354">
       <c r="B354" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
@@ -22397,22 +22397,22 @@
     <row r="355">
       <c r="B355" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
@@ -22456,22 +22456,22 @@
     <row r="356">
       <c r="B356" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
@@ -22515,22 +22515,22 @@
     <row r="357">
       <c r="B357" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
@@ -22574,22 +22574,22 @@
     <row r="358">
       <c r="B358" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
@@ -22633,22 +22633,22 @@
     <row r="359">
       <c r="B359" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
@@ -22692,22 +22692,22 @@
     <row r="360">
       <c r="B360" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
@@ -22751,22 +22751,22 @@
     <row r="361">
       <c r="B361" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
@@ -22810,22 +22810,22 @@
     <row r="362">
       <c r="B362" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
@@ -22869,22 +22869,22 @@
     <row r="363">
       <c r="B363" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F363" t="inlineStr">
@@ -22928,22 +22928,22 @@
     <row r="364">
       <c r="B364" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
@@ -22987,22 +22987,22 @@
     <row r="365">
       <c r="B365" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
@@ -23046,22 +23046,22 @@
     <row r="366">
       <c r="B366" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>1833025</t>
+          <t>1833026</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
         <is>
-          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 개인형)</t>
+          <t>한화생명 Wealth직장인연금보험 무배당 (종신연금형 신부부형)</t>
         </is>
       </c>
       <c r="F366" t="inlineStr">
